--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -655,7 +655,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -663,7 +663,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，直接持有发行人 5%以上股份的其他主要股东如下表所示：</t>
+          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>中科星图</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -693,7 +693,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，直接持有发行人 5%以上股份的其他主要股东如下表所示：</t>
+          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -723,7 +723,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，直接持有发行人 5%以上股份的其他主要股东如下表所示：</t>
+          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
         </is>
       </c>
     </row>
@@ -767,21 +767,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2023年5月定向发行后股权结构</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>8250</v>
-      </c>
+          <t>报告期初（2021年1月1日）股权结构</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>中科星图</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -789,7 +787,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，直接持有发行人 5%以上股份的其他主要股东如下表所示：</t>
+          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
         </is>
       </c>
     </row>
@@ -799,21 +797,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2023年5月定向发行后股权结构</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>8250</v>
-      </c>
+          <t>报告期初（2021年1月1日）股权结构</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>中科星图</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -821,7 +817,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，直接持有发行人 5%以上股份的其他主要股东如下表所示：</t>
+          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
         </is>
       </c>
     </row>
@@ -831,21 +827,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>t0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2023年5月定向发行后股权结构</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8250</v>
-      </c>
+          <t>报告期初（2021年1月1日）股权结构</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>中科星图</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -853,7 +847,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>截至本招股说明书签署日，直接持有发行人 5%以上股份的其他主要股东如下表所示：</t>
+          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -628,9 +628,13 @@
           <t>中科星图</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>3825</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
@@ -658,9 +662,13 @@
           <t>中科星图</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>3825</v>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
@@ -688,9 +696,13 @@
           <t>中科星图</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>3825</v>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
@@ -718,9 +730,13 @@
           <t>中科星图</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>3825</v>
+      </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
@@ -754,7 +770,9 @@
         <v>3825</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，公司总股本为 82,500,000 股，中科星图持有公司 38,250,000 股，持股比例为46.36%</t>
@@ -782,9 +800,13 @@
           <t>中科星图</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>3825</v>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
@@ -812,9 +834,13 @@
           <t>中科星图</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>3825</v>
+      </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
@@ -842,9 +868,13 @@
           <t>中科星图</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>3825</v>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>46.36</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,8 +622,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -631,7 +630,6 @@
       <c r="G2" t="n">
         <v>3825</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>46.36</v>
       </c>
@@ -655,8 +653,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -665,7 +661,6 @@
       <c r="G3" t="n">
         <v>3825</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>46.36</v>
       </c>
@@ -689,8 +684,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -699,7 +692,6 @@
       <c r="G4" t="n">
         <v>3825</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>46.36</v>
       </c>
@@ -723,8 +715,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -733,7 +723,6 @@
       <c r="G5" t="n">
         <v>3825</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>46.36</v>
       </c>
@@ -760,7 +749,6 @@
       <c r="D6" t="n">
         <v>8250</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -769,7 +757,6 @@
       <c r="G6" t="n">
         <v>3825</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>46.36</v>
       </c>
@@ -793,8 +780,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -803,7 +788,6 @@
       <c r="G7" t="n">
         <v>3825</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>46.36</v>
       </c>
@@ -827,8 +811,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -837,7 +819,6 @@
       <c r="G8" t="n">
         <v>3825</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>46.36</v>
       </c>
@@ -861,8 +842,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -871,7 +850,6 @@
       <c r="G9" t="n">
         <v>3825</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>46.36</v>
       </c>
@@ -898,7 +876,6 @@
       <c r="D10" t="n">
         <v>8250</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>策星银河</t>
@@ -907,8 +884,6 @@
       <c r="G10" t="n">
         <v>279</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>策星银河持有发行人 2,790,000 股股份，持股比例为3.38%</t>
@@ -932,7 +907,6 @@
       <c r="D11" t="n">
         <v>8250</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>策星逐日</t>
@@ -941,8 +915,6 @@
       <c r="G11" t="n">
         <v>171</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>策星逐日持有发行人 1,710,000 股股份，持股比例为2.07%</t>
@@ -966,7 +938,6 @@
       <c r="D12" t="n">
         <v>8250</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>幸福二期</t>
@@ -975,11 +946,337 @@
       <c r="G12" t="n">
         <v>300</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>幸福二期持有发行人 3,000,000 股股份，持股比例为3.64%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴流量3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权存量11条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>字段类型+t0存在检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>26775</v>
+      </c>
+      <c r="E4" t="n">
+        <v>750</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27525</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4575</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-22950</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>中科星图</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3825</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3825</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3825</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>171</v>
+      </c>
+      <c r="F7" t="n">
+        <v>171</v>
+      </c>
+      <c r="G7" t="n">
+        <v>171</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>279</v>
+      </c>
+      <c r="F8" t="n">
+        <v>279</v>
+      </c>
+      <c r="G8" t="n">
+        <v>279</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -622,6 +621,8 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -630,6 +631,7 @@
       <c r="G2" t="n">
         <v>3825</v>
       </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>46.36</v>
       </c>
@@ -653,6 +655,8 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -661,6 +665,7 @@
       <c r="G3" t="n">
         <v>3825</v>
       </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>46.36</v>
       </c>
@@ -684,6 +689,8 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -692,6 +699,7 @@
       <c r="G4" t="n">
         <v>3825</v>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>46.36</v>
       </c>
@@ -715,6 +723,8 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -723,6 +733,7 @@
       <c r="G5" t="n">
         <v>3825</v>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>46.36</v>
       </c>
@@ -749,6 +760,7 @@
       <c r="D6" t="n">
         <v>8250</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -757,6 +769,7 @@
       <c r="G6" t="n">
         <v>3825</v>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>46.36</v>
       </c>
@@ -780,6 +793,8 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -788,6 +803,7 @@
       <c r="G7" t="n">
         <v>3825</v>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>46.36</v>
       </c>
@@ -811,6 +827,8 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -819,6 +837,7 @@
       <c r="G8" t="n">
         <v>3825</v>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>46.36</v>
       </c>
@@ -842,6 +861,8 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -850,6 +871,7 @@
       <c r="G9" t="n">
         <v>3825</v>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>46.36</v>
       </c>
@@ -876,6 +898,7 @@
       <c r="D10" t="n">
         <v>8250</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>策星银河</t>
@@ -884,6 +907,8 @@
       <c r="G10" t="n">
         <v>279</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>策星银河持有发行人 2,790,000 股股份，持股比例为3.38%</t>
@@ -907,6 +932,7 @@
       <c r="D11" t="n">
         <v>8250</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>策星逐日</t>
@@ -915,6 +941,8 @@
       <c r="G11" t="n">
         <v>171</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>策星逐日持有发行人 1,710,000 股股份，持股比例为2.07%</t>
@@ -938,6 +966,7 @@
       <c r="D12" t="n">
         <v>8250</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>幸福二期</t>
@@ -946,337 +975,11 @@
       <c r="G12" t="n">
         <v>300</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>幸福二期持有发行人 3,000,000 股股份，持股比例为3.64%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量11条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>字段类型+t0存在检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>26775</v>
-      </c>
-      <c r="E4" t="n">
-        <v>750</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27525</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4575</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-22950</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3825</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3825</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3825</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>幸福二期</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" t="n">
-        <v>300</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>策星逐日</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>171</v>
-      </c>
-      <c r="F7" t="n">
-        <v>171</v>
-      </c>
-      <c r="G7" t="n">
-        <v>171</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>策星银河</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>279</v>
-      </c>
-      <c r="F8" t="n">
-        <v>279</v>
-      </c>
-      <c r="G8" t="n">
-        <v>279</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,8 +622,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -631,7 +630,6 @@
       <c r="G2" t="n">
         <v>3825</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>46.36</v>
       </c>
@@ -655,8 +653,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -665,7 +661,6 @@
       <c r="G3" t="n">
         <v>3825</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>46.36</v>
       </c>
@@ -689,8 +684,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -699,7 +692,6 @@
       <c r="G4" t="n">
         <v>3825</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>46.36</v>
       </c>
@@ -723,8 +715,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -733,7 +723,6 @@
       <c r="G5" t="n">
         <v>3825</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>46.36</v>
       </c>
@@ -760,7 +749,6 @@
       <c r="D6" t="n">
         <v>8250</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -769,7 +757,6 @@
       <c r="G6" t="n">
         <v>3825</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>46.36</v>
       </c>
@@ -793,8 +780,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -803,7 +788,6 @@
       <c r="G7" t="n">
         <v>3825</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>46.36</v>
       </c>
@@ -827,8 +811,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -837,7 +819,6 @@
       <c r="G8" t="n">
         <v>3825</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>46.36</v>
       </c>
@@ -861,8 +842,6 @@
           <t>报告期初（2021年1月1日）股权结构</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -871,7 +850,6 @@
       <c r="G9" t="n">
         <v>3825</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>46.36</v>
       </c>
@@ -898,7 +876,6 @@
       <c r="D10" t="n">
         <v>8250</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>策星银河</t>
@@ -907,8 +884,6 @@
       <c r="G10" t="n">
         <v>279</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>策星银河持有发行人 2,790,000 股股份，持股比例为3.38%</t>
@@ -932,7 +907,6 @@
       <c r="D11" t="n">
         <v>8250</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>策星逐日</t>
@@ -941,8 +915,6 @@
       <c r="G11" t="n">
         <v>171</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>策星逐日持有发行人 1,710,000 股股份，持股比例为2.07%</t>
@@ -966,7 +938,6 @@
       <c r="D12" t="n">
         <v>8250</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>幸福二期</t>
@@ -975,11 +946,333 @@
       <c r="G12" t="n">
         <v>300</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>幸福二期持有发行人 3,000,000 股股份，持股比例为3.64%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量11条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>26775</v>
+      </c>
+      <c r="E4" t="n">
+        <v>750</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27525</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4575</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-22950</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>中科星图</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3825</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3825</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3825</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>策星逐日</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>171</v>
+      </c>
+      <c r="F7" t="n">
+        <v>171</v>
+      </c>
+      <c r="G7" t="n">
+        <v>171</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>279</v>
+      </c>
+      <c r="F8" t="n">
+        <v>279</v>
+      </c>
+      <c r="G8" t="n">
+        <v>279</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +479,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>本次股票发行股数为 7,500,000 股，每股价格为人民币 6.30元，募集资金总额为47,250,000.00 元。</t>
+          <t>Markdown提取: 策星银河认购2,790,000股/17,577,000元</t>
         </is>
       </c>
     </row>
@@ -509,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>本次股票发行股数为 7,500,000 股，每股价格为人民币 6.30元，募集资金总额为47,250,000.00 元。</t>
+          <t>Markdown提取: 策星逐日认购1,710,000股/10,773,000元</t>
         </is>
       </c>
     </row>
@@ -538,7 +537,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>本次股票发行股数为 7,500,000 股，每股价格为人民币 6.30元，募集资金总额为47,250,000.00 元。</t>
+          <t>Markdown提取: 幸福二期认购3,000,000股/18,900,000元</t>
         </is>
       </c>
     </row>
@@ -553,423 +552,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>PDF页码</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股权结构口径</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>总股本(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>总出资额(万元注册资本)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>股东名称</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>持股数(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>出资额(万元注册资本)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>持股比例</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>原文证据</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>报告期初（2021年1月1日）股权结构</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I2" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>报告期初（2021年1月1日）股权结构</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I3" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>报告期初（2021年1月1日）股权结构</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I4" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>报告期初（2021年1月1日）股权结构</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I5" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2023年5月定向发行后股权结构</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>8250</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I6" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，公司总股本为 82,500,000 股，中科星图持有公司 38,250,000 股，持股比例为46.36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>报告期初（2021年1月1日）股权结构</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I7" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>47</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>报告期初（2021年1月1日）股权结构</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I8" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>47</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t0</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>报告期初（2021年1月1日）股权结构</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>中科星图</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>3825</v>
-      </c>
-      <c r="I9" t="n">
-        <v>46.36</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>截至本招股说明书签署日，中科星图持有公司 38,250,000 股，持股比例为46.36%，为公司的控股股东。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>47</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2023年5月定向发行后股权结构</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>8250</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>策星银河</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>279</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>策星银河持有发行人 2,790,000 股股份，持股比例为3.38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>47</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2023年5月定向发行后股权结构</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>8250</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>策星逐日</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>171</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>策星逐日持有发行人 1,710,000 股股份，持股比例为2.07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>47</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2023年5月定向发行后股权结构</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>8250</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>幸福二期</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>300</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>幸福二期持有发行人 3,000,000 股股份，持股比例为3.64%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>检查类型</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -979,300 +568,294 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股权结构口径</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>上一时点</t>
+          <t>总股本(万股)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>本次变化</t>
+          <t>总出资额(万元注册资本)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>预期值</t>
+          <t>股东名称</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>PDF值</t>
+          <t>持股数(万股)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>差额</t>
+          <t>出资额(万元注册资本)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>校验结果</t>
+          <t>持股比例</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>原文证据</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="A2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>发行前</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8250</v>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>中科星图</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3825</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
+      <c r="I2" t="n">
+        <v>46.36</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>字段类型+非空检查通过</t>
+          <t>Markdown发行前后表: 中科星图发行前38250000股/46.36%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="A3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>发行前</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>存量11条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8250</v>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>策星九天</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2345.0781</v>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
+      <c r="I3" t="n">
+        <v>28.43</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>t0存在+类型检查通过</t>
+          <t>Markdown发行前后表: 策星九天发行前23450781股/28.43%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
+      <c r="A4" t="n">
+        <v>47</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t0-&gt;t1</t>
+          <t>发行前</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>总股本</t>
+          <t>本次发行前公司股权结构</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26775</v>
-      </c>
-      <c r="E4" t="n">
-        <v>750</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27525</v>
+        <v>8250</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>幸福一期</t>
+        </is>
       </c>
       <c r="G4" t="n">
-        <v>4575</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-22950</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>917.4219000000001</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Markdown发行前后表: 幸福一期发行前9174219股/11.12%</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
+      <c r="A5" t="n">
+        <v>47</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t0-&gt;t1</t>
+          <t>发行前</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>中科星图</t>
+          <t>本次发行前公司股权结构</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3825</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3825</v>
+        <v>8250</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>策星揽月</t>
+        </is>
       </c>
       <c r="G5" t="n">
-        <v>3825</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>412.5</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Markdown发行前后表: 策星揽月发行前4125000股/5.0%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
+      <c r="A6" t="n">
+        <v>47</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t0-&gt;t1</t>
+          <t>发行前</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>幸福二期</t>
         </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>300</v>
       </c>
       <c r="G6" t="n">
         <v>300</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>3.64</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>Markdown发行前后表: 幸福二期发行前3000000股/3.64%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
+      <c r="A7" t="n">
+        <v>47</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t0-&gt;t1</t>
+          <t>发行前</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>策星银河</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>279</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Markdown发行前后表: 策星银河发行前2790000股/3.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>发行前</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>本次发行前公司股权结构</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>策星逐日</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="G8" t="n">
         <v>171</v>
       </c>
-      <c r="F7" t="n">
-        <v>171</v>
-      </c>
-      <c r="G7" t="n">
-        <v>171</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>策星银河</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>279</v>
-      </c>
-      <c r="F8" t="n">
-        <v>279</v>
-      </c>
-      <c r="G8" t="n">
-        <v>279</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>2.07</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>Markdown发行前后表: 策星逐日发行前1710000股/2.07%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,7 +625,6 @@
       <c r="D2" t="n">
         <v>8250</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -633,7 +633,6 @@
       <c r="G2" t="n">
         <v>3825</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>46.36</v>
       </c>
@@ -660,7 +659,6 @@
       <c r="D3" t="n">
         <v>8250</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>策星九天</t>
@@ -669,7 +667,6 @@
       <c r="G3" t="n">
         <v>2345.0781</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>28.43</v>
       </c>
@@ -696,7 +693,6 @@
       <c r="D4" t="n">
         <v>8250</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>幸福一期</t>
@@ -705,7 +701,6 @@
       <c r="G4" t="n">
         <v>917.4219000000001</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>11.12</v>
       </c>
@@ -732,7 +727,6 @@
       <c r="D5" t="n">
         <v>8250</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>策星揽月</t>
@@ -741,7 +735,6 @@
       <c r="G5" t="n">
         <v>412.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>5</v>
       </c>
@@ -768,7 +761,6 @@
       <c r="D6" t="n">
         <v>8250</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>幸福二期</t>
@@ -777,7 +769,6 @@
       <c r="G6" t="n">
         <v>300</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>3.64</v>
       </c>
@@ -804,7 +795,6 @@
       <c r="D7" t="n">
         <v>8250</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>策星银河</t>
@@ -813,7 +803,6 @@
       <c r="G7" t="n">
         <v>279</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>3.38</v>
       </c>
@@ -840,7 +829,6 @@
       <c r="D8" t="n">
         <v>8250</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>策星逐日</t>
@@ -849,7 +837,6 @@
       <c r="G8" t="n">
         <v>171</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>2.07</v>
       </c>
@@ -858,6 +845,162 @@
           <t>Markdown发行前后表: 策星逐日发行前1710000股/2.07%</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量7条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>发行前</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7股东</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,6 +624,7 @@
       <c r="D2" t="n">
         <v>8250</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -633,6 +633,7 @@
       <c r="G2" t="n">
         <v>3825</v>
       </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>46.36</v>
       </c>
@@ -659,6 +660,7 @@
       <c r="D3" t="n">
         <v>8250</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>策星九天</t>
@@ -667,6 +669,7 @@
       <c r="G3" t="n">
         <v>2345.0781</v>
       </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>28.43</v>
       </c>
@@ -693,6 +696,7 @@
       <c r="D4" t="n">
         <v>8250</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>幸福一期</t>
@@ -701,6 +705,7 @@
       <c r="G4" t="n">
         <v>917.4219000000001</v>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>11.12</v>
       </c>
@@ -727,6 +732,7 @@
       <c r="D5" t="n">
         <v>8250</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>策星揽月</t>
@@ -735,6 +741,7 @@
       <c r="G5" t="n">
         <v>412.5</v>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>5</v>
       </c>
@@ -761,6 +768,7 @@
       <c r="D6" t="n">
         <v>8250</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>幸福二期</t>
@@ -769,6 +777,7 @@
       <c r="G6" t="n">
         <v>300</v>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>3.64</v>
       </c>
@@ -795,6 +804,7 @@
       <c r="D7" t="n">
         <v>8250</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>策星银河</t>
@@ -803,6 +813,7 @@
       <c r="G7" t="n">
         <v>279</v>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>3.38</v>
       </c>
@@ -829,6 +840,7 @@
       <c r="D8" t="n">
         <v>8250</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>策星逐日</t>
@@ -837,6 +849,7 @@
       <c r="G8" t="n">
         <v>171</v>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>2.07</v>
       </c>
@@ -845,162 +858,6 @@
           <t>Markdown发行前后表: 策星逐日发行前1710000股/2.07%</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量7条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>发行前</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>7股东</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>8250</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -624,7 +625,6 @@
       <c r="D2" t="n">
         <v>8250</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -633,7 +633,6 @@
       <c r="G2" t="n">
         <v>3825</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>46.36</v>
       </c>
@@ -660,7 +659,6 @@
       <c r="D3" t="n">
         <v>8250</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>策星九天</t>
@@ -669,7 +667,6 @@
       <c r="G3" t="n">
         <v>2345.0781</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>28.43</v>
       </c>
@@ -696,7 +693,6 @@
       <c r="D4" t="n">
         <v>8250</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>幸福一期</t>
@@ -705,7 +701,6 @@
       <c r="G4" t="n">
         <v>917.4219000000001</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>11.12</v>
       </c>
@@ -732,7 +727,6 @@
       <c r="D5" t="n">
         <v>8250</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>策星揽月</t>
@@ -741,7 +735,6 @@
       <c r="G5" t="n">
         <v>412.5</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>5</v>
       </c>
@@ -768,7 +761,6 @@
       <c r="D6" t="n">
         <v>8250</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>幸福二期</t>
@@ -777,7 +769,6 @@
       <c r="G6" t="n">
         <v>300</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>3.64</v>
       </c>
@@ -804,7 +795,6 @@
       <c r="D7" t="n">
         <v>8250</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>策星银河</t>
@@ -813,7 +803,6 @@
       <c r="G7" t="n">
         <v>279</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>3.38</v>
       </c>
@@ -840,7 +829,6 @@
       <c r="D8" t="n">
         <v>8250</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>策星逐日</t>
@@ -849,13 +837,149 @@
       <c r="G8" t="n">
         <v>171</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>2.07</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Markdown发行前后表: 策星逐日发行前1710000股/2.07%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴3条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量7条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让2条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>发行前</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7股东</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>比例合计100.00%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,6 +624,7 @@
       <c r="D2" t="n">
         <v>8250</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>中科星图</t>
@@ -633,6 +633,7 @@
       <c r="G2" t="n">
         <v>3825</v>
       </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>46.36</v>
       </c>
@@ -659,6 +660,7 @@
       <c r="D3" t="n">
         <v>8250</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>策星九天</t>
@@ -667,6 +669,7 @@
       <c r="G3" t="n">
         <v>2345.0781</v>
       </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>28.43</v>
       </c>
@@ -693,6 +696,7 @@
       <c r="D4" t="n">
         <v>8250</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>幸福一期</t>
@@ -701,6 +705,7 @@
       <c r="G4" t="n">
         <v>917.4219000000001</v>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>11.12</v>
       </c>
@@ -727,6 +732,7 @@
       <c r="D5" t="n">
         <v>8250</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>策星揽月</t>
@@ -735,6 +741,7 @@
       <c r="G5" t="n">
         <v>412.5</v>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>5</v>
       </c>
@@ -761,6 +768,7 @@
       <c r="D6" t="n">
         <v>8250</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>幸福二期</t>
@@ -769,6 +777,7 @@
       <c r="G6" t="n">
         <v>300</v>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>3.64</v>
       </c>
@@ -795,6 +804,7 @@
       <c r="D7" t="n">
         <v>8250</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>策星银河</t>
@@ -803,6 +813,7 @@
       <c r="G7" t="n">
         <v>279</v>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>3.38</v>
       </c>
@@ -829,6 +840,7 @@
       <c r="D8" t="n">
         <v>8250</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>策星逐日</t>
@@ -837,149 +849,13 @@
       <c r="G8" t="n">
         <v>171</v>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>2.07</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Markdown发行前后表: 策星逐日发行前1710000股/2.07%</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴3条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量7条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>转让2条</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>发行前</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>7股东</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>比例合计100.00%</t>
         </is>
       </c>
     </row>
